--- a/forms/trg/Formulir_TRG_icchealth.xlsx
+++ b/forms/trg/Formulir_TRG_icchealth.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B42)</f>
+        <f>COUNTA(Anggota!B5:B43)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F42)</f>
+        <f>COUNTA(Anggota!F5:F43)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,16 +925,16 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Rizky Chaeraty Syam</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
+          <t>Sudirman Nasir</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Rosa Ayu</t>
+          <t>Rizky Chaeraty Syam</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Indra Fajarwati</t>
+          <t>Rosa Ayu</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Shanti Riskiyani</t>
+          <t>Indra Fajarwati</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Ilham Alimuddin</t>
+          <t>Shanti Riskiyani</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rijal Idrus</t>
+          <t>Ilham Alimuddin</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1099,19 +1099,15 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Sharyn Davies</t>
+          <t>Rijal Idrus</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Monash University, Australia</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
@@ -1132,12 +1128,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Becky Batagol</t>
+          <t>Sharyn Davies</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1165,17 +1161,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Yasemin Didem Aktas</t>
+          <t>Becky Batagol</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>University College London (UCL), UK</t>
+          <t>Monash University, Australia</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1198,17 +1194,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ian Wilson</t>
+          <t>Yasemin Didem Aktas</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Murdoch University, Australia</t>
+          <t>University College London (UCL), UK</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1231,17 +1227,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Youdiil Ophinni</t>
+          <t>Ian Wilson</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Kyoto University, Japan</t>
+          <t>Murdoch University, Australia</t>
         </is>
       </c>
       <c r="E15" s="11" t="n"/>
@@ -1264,12 +1260,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Chika Yamada</t>
+          <t>Youdiil Ophinni</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1297,15 +1293,19 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Febriani Tenri Sa’nna</t>
+          <t>Chika Yamada</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Kyoto University, Japan</t>
+        </is>
+      </c>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Nurmala Sari</t>
+          <t>Febriani Tenri Sa’nna</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rachmat</t>
+          <t>Nurmala Sari</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Ryza Jazid Baharuddin Nur</t>
+          <t>Muhammad Rachmat</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Agum Trianto Gunawan</t>
+          <t>Ryza Jazid Baharuddin Nur</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Rafika Nurul Hamdani Ramli</t>
+          <t>Agum Trianto Gunawan</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Nabila May Sweetha</t>
+          <t>Rafika Nurul Hamdani Ramli</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ulil Ahsan</t>
+          <t>Nabila May Sweetha</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Nur Isdah Idris</t>
+          <t>Muhammad Ulil Ahsan</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Salman Samir</t>
+          <t>Nur Isdah Idris</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Betrin Natasya</t>
+          <t>Salman Samir</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1616,20 +1616,16 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Fadhilah Trya Wulandari</t>
+          <t>Betrin Natasya</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Doctoral Student</t>
-        </is>
-      </c>
+      <c r="E28" s="11" t="n"/>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="12" t="n"/>
       <c r="H28" s="12" t="n"/>
@@ -1649,18 +1645,18 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Alifiah Sabila</t>
+          <t>Fadhilah Trya Wulandari</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Undergraduate Student</t>
+          <t>Doctoral Student</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1682,18 +1678,18 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Marni</t>
+          <t>Alifiah Sabila</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student</t>
+          <t>Undergraduate Student</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -1713,10 +1709,26 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="11" t="n"/>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Marni</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Doctoral Student</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Climate crisis is a health crisis. Climate change facilitates various climate-induced disasters and these disasters damage livelihood and basic facilities and in turn disturb people’s health and wellbeing. Climate crisis and climate-induced disasters facilitate various health problems, exacerbate communicable and non- communicable diseases and worsen people’s health and wellbeing, particularly vulnerable population.</t>
+        </is>
+      </c>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="n"/>
@@ -1724,7 +1736,11 @@
       <c r="J31" s="12" t="n"/>
       <c r="K31" s="12" t="n"/>
       <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1913,15 +1929,32 @@
       <c r="L42" s="12" t="n"/>
       <c r="M42" s="12" t="n"/>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_icchealth.xlsx
+++ b/forms/trg/Formulir_TRG_icchealth.xlsx
@@ -928,7 +928,11 @@
           <t>Sudirman Nasir</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
